--- a/temp_upload.xlsx
+++ b/temp_upload.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F15169FF-E1E6-480E-B689-4CED8604EF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anand Swarup\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DC386B-EF65-4D18-A2A6-DF6491AA447F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="50">
   <si>
     <t>customer_id</t>
   </si>
@@ -69,19 +77,19 @@
     <t>country_code</t>
   </si>
   <si>
-    <t>vinayak</t>
-  </si>
-  <si>
-    <t>vinayak_sharma@technologymindz.com</t>
+    <t>Alice1 Johnson</t>
+  </si>
+  <si>
+    <t>alice.johnson@example.com</t>
   </si>
   <si>
     <t>Alice is interested in the premium package that includes advanced analytics, priority support, and additional storage capacity. She wants a detailed demo before making the decision.</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>ABC Company</t>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>A Company</t>
   </si>
   <si>
     <t>Texas, USA</t>
@@ -96,47 +104,101 @@
     <t>bob.smith@example.com</t>
   </si>
   <si>
+    <t>"nan
+[2025-08-23 13:05:56] The customer, Bob Smith, is from the Automobile industry and wants to know how Technology Mindz can help him grow his company. The agent explains the services offered by Technology Mindz, including Salesforce implementation, robotic process automation, AI and data analytics, and cybersecurity solutions. The customer schedules a meeting with the agent for the next day at 5 p.m.
+[2025-08-23 13:22:09] No summary available. Conversation transcript missing."</t>
+  </si>
+  <si>
+    <t>B Company</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Automobile</t>
+  </si>
+  <si>
+    <t>charlie.brown@example.com</t>
+  </si>
+  <si>
+    <t>Charlie is evaluating enterprise-level solutions with a strong emphasis on scalability, integration with his existing ERP system, and compliance with international data protection regulations. He also needs a custom training program for his team.</t>
+  </si>
+  <si>
+    <t>"Charlie has shown strong interest in a long-term partnership if the enterprise solution aligns with his company’s compliance and integration needs. He mentioned that decision-making will involve multiple stakeholders, and the procurement cycle might take up to three months. We should prepare detailed documentation, case studies, and a tailored presentation for his board of directors.
+[2025-08-23 13:13:59] No summary available. Conversation transcript missing."</t>
+  </si>
+  <si>
+    <t>C Company</t>
+  </si>
+  <si>
+    <t>Berlin, Germany</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Vinayak</t>
+  </si>
+  <si>
+    <t>D Company</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>E Company</t>
+  </si>
+  <si>
+    <t>Francis</t>
+  </si>
+  <si>
+    <t>F Company</t>
+  </si>
+  <si>
+    <t>Gargi</t>
+  </si>
+  <si>
+    <t>He mentioned that decision-making will involve multiple stakeholders, and the procurement cycle might take up to three months.</t>
+  </si>
+  <si>
+    <t>G Company</t>
+  </si>
+  <si>
+    <t>Hailey</t>
+  </si>
+  <si>
+    <t>We should prepare detailed documentation, case studies, and a tailored presentation for his board of directors.</t>
+  </si>
+  <si>
+    <t>H Company</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
+  </si>
+  <si>
     <t>Bob is looking for a basic support plan primarily to cover troubleshooting and regular software updates. He has budget constraints and does not want advanced features right now.</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>some company</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Automobile</t>
-  </si>
-  <si>
-    <t>vipul</t>
-  </si>
-  <si>
-    <t>Charlie is evaluating enterprise-level solutions with a strong emphasis on scalability, integration with his existing ERP system, and compliance with international data protection regulations. He also needs a custom training program for his team.</t>
-  </si>
-  <si>
-    <t>Charlie has shown strong interest in a long-term partnership if the enterprise solution aligns with his company’s compliance and integration needs. He mentioned that decision-making will involve multiple stakeholders, and the procurement cycle might take up to three months. We should prepare detailed documentation, case studies, and a tailored presentation for his board of directors.</t>
-  </si>
-  <si>
-    <t>XYZ Company Ltd.</t>
-  </si>
-  <si>
-    <t>Berlin, Germany</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Vivek Gupta</t>
+    <t>I Company</t>
+  </si>
+  <si>
+    <t>Jacob</t>
+  </si>
+  <si>
+    <t>Charlie has shown strong interest in a long-term partnership if the enterprise solution aligns with his company’s compliance and integration needs.</t>
+  </si>
+  <si>
+    <t>J Company</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,16 +206,85 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF001D35"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -161,12 +292,117 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,69 +737,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.26953125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="27.54296875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="68.453125" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="51.54296875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="17.26953125" style="18" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" customWidth="1"/>
+    <col min="11" max="11" width="16.26953125" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2">
+    <row r="2" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C2">
-        <v>8107331777</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="16"/>
       <c r="I2" t="s">
         <v>16</v>
       </c>
@@ -573,91 +820,278 @@
       <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="5">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3">
+    <row r="3" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C3">
-        <v>-934</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="8">
+        <v>8146994031</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="16"/>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="145" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="D4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L3">
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="16"/>
+      <c r="I4" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="5">
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="29">
+        <v>7878994162</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="44" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="43.5" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="43.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="58" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4">
-        <v>8407917181</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
-        <v>9001985764</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5">
+      <c r="F11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="5">
         <v>91</v>
       </c>
     </row>

--- a/temp_upload.xlsx
+++ b/temp_upload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anand Swarup\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DC386B-EF65-4D18-A2A6-DF6491AA447F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E869BAA-2EA1-4789-A3C6-08E3B0B4A8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
   <si>
     <t>customer_id</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Bob Smith</t>
   </si>
   <si>
     <t>bob.smith@example.com</t>
@@ -192,13 +189,19 @@
   </si>
   <si>
     <t>J Company</t>
+  </si>
+  <si>
+    <t>anand_swarup@technologymindz.com</t>
+  </si>
+  <si>
+    <t>Anand Swarup</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,6 +266,14 @@
       <name val="Aptos Narrow"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -321,10 +332,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -403,8 +415,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -829,30 +845,30 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8">
         <v>8146994031</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>20</v>
+      <c r="D3" s="30" t="s">
+        <v>49</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" s="16"/>
       <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
       </c>
       <c r="L3" s="5">
         <v>91</v>
@@ -864,26 +880,26 @@
       </c>
       <c r="B4" s="21"/>
       <c r="D4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
       </c>
       <c r="L4" s="5">
         <v>91</v>
@@ -894,10 +910,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="29">
-        <v>7878994162</v>
+        <v>8107061392</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>13</v>
@@ -906,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -923,23 +939,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="27" t="s">
-        <v>35</v>
-      </c>
       <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
         <v>23</v>
-      </c>
-      <c r="K6" t="s">
-        <v>24</v>
       </c>
       <c r="L6" s="5">
         <v>91</v>
@@ -950,23 +966,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s">
         <v>29</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
       </c>
       <c r="L7" s="5">
         <v>91</v>
@@ -977,20 +993,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="27" t="s">
         <v>39</v>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>40</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -1004,29 +1020,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="27" t="s">
-        <v>43</v>
-      </c>
       <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
         <v>23</v>
-      </c>
-      <c r="K9" t="s">
-        <v>24</v>
       </c>
       <c r="L9" s="5">
         <v>91</v>
@@ -1037,26 +1053,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>46</v>
-      </c>
       <c r="J10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" t="s">
         <v>29</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
       </c>
       <c r="L10" s="5">
         <v>91</v>
@@ -1067,23 +1083,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G11" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="27" t="s">
         <v>48</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>49</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1096,6 +1112,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{962D2074-1D24-4143-B47E-20143E2E128C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/temp_upload.xlsx
+++ b/temp_upload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anand Swarup\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E869BAA-2EA1-4789-A3C6-08E3B0B4A8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6F4C62-9959-4DAC-A015-63BFBE437941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
   <si>
     <t>customer_id</t>
   </si>
@@ -99,11 +99,6 @@
   </si>
   <si>
     <t>bob.smith@example.com</t>
-  </si>
-  <si>
-    <t>"nan
-[2025-08-23 13:05:56] The customer, Bob Smith, is from the Automobile industry and wants to know how Technology Mindz can help him grow his company. The agent explains the services offered by Technology Mindz, including Salesforce implementation, robotic process automation, AI and data analytics, and cybersecurity solutions. The customer schedules a meeting with the agent for the next day at 5 p.m.
-[2025-08-23 13:22:09] No summary available. Conversation transcript missing."</t>
   </si>
   <si>
     <t>B Company</t>
@@ -840,35 +835,33 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="8">
         <v>8146994031</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>20</v>
-      </c>
+      <c r="G3" s="16"/>
       <c r="H3" s="16"/>
       <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
       </c>
       <c r="L3" s="5">
         <v>91</v>
@@ -880,26 +873,26 @@
       </c>
       <c r="B4" s="21"/>
       <c r="D4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
       </c>
       <c r="L4" s="5">
         <v>91</v>
@@ -910,7 +903,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="29">
         <v>8107061392</v>
@@ -919,10 +912,10 @@
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -939,23 +932,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="13" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="27" t="s">
-        <v>34</v>
-      </c>
       <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
         <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
       </c>
       <c r="L6" s="5">
         <v>91</v>
@@ -966,23 +959,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s">
         <v>28</v>
-      </c>
-      <c r="K7" t="s">
-        <v>29</v>
       </c>
       <c r="L7" s="5">
         <v>91</v>
@@ -993,20 +986,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="27" t="s">
         <v>38</v>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>39</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -1020,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="13" t="s">
@@ -1030,19 +1023,19 @@
         <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="27" t="s">
-        <v>42</v>
-      </c>
       <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
         <v>22</v>
-      </c>
-      <c r="K9" t="s">
-        <v>23</v>
       </c>
       <c r="L9" s="5">
         <v>91</v>
@@ -1053,26 +1046,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>45</v>
-      </c>
       <c r="J10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" t="s">
         <v>28</v>
-      </c>
-      <c r="K10" t="s">
-        <v>29</v>
       </c>
       <c r="L10" s="5">
         <v>91</v>
@@ -1083,23 +1076,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="I11" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
